--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_atacama.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_atacama.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>31.59517776795939</v>
+      </c>
+      <c r="C2">
         <v>20.61531248027556</v>
-      </c>
-      <c r="C2">
-        <v>31.59517776795939</v>
       </c>
       <c r="D2">
         <v>4.850763241919259</v>
       </c>
       <c r="E2">
-        <v>13.54394985960215</v>
+        <v>20.75755601104226</v>
       </c>
       <c r="F2">
         <v>65.69849412935559</v>
       </c>
       <c r="G2">
-        <v>20.75755601104226</v>
+        <v>13.54394985960215</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>33.25469843516552</v>
+      </c>
+      <c r="C3">
         <v>24.81717386175985</v>
-      </c>
-      <c r="C3">
-        <v>33.25469843516552</v>
       </c>
       <c r="D3">
         <v>4.029467680608365</v>
       </c>
       <c r="E3">
+        <v>21.03770769077704</v>
+      </c>
+      <c r="F3">
+        <v>63.26236195403443</v>
+      </c>
+      <c r="G3">
         <v>15.69993035518854</v>
-      </c>
-      <c r="F3">
-        <v>63.26236195403442</v>
-      </c>
-      <c r="G3">
-        <v>21.03770769077703</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>40.12846927645134</v>
+      </c>
+      <c r="C4">
         <v>19.90061810689613</v>
-      </c>
-      <c r="C4">
-        <v>40.12846927645134</v>
       </c>
       <c r="D4">
         <v>5.024969549330085</v>
       </c>
       <c r="E4">
-        <v>12.43562556800969</v>
+        <v>25.07573462587095</v>
       </c>
       <c r="F4">
         <v>62.48863980611936</v>
       </c>
       <c r="G4">
-        <v>25.07573462587095</v>
+        <v>12.43562556800969</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>32.21618022417046</v>
+      </c>
+      <c r="C5">
         <v>26.75618688269892</v>
-      </c>
-      <c r="C5">
-        <v>32.21618022417046</v>
       </c>
       <c r="D5">
         <v>3.737453338863542</v>
       </c>
       <c r="E5">
+        <v>20.2652705061082</v>
+      </c>
+      <c r="F5">
+        <v>62.90401396160559</v>
+      </c>
+      <c r="G5">
         <v>16.83071553228621</v>
-      </c>
-      <c r="F5">
-        <v>62.90401396160558</v>
-      </c>
-      <c r="G5">
-        <v>20.2652705061082</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>34.34961493828463</v>
+      </c>
+      <c r="C6">
         <v>19.14758940816542</v>
-      </c>
-      <c r="C6">
-        <v>34.34961493828463</v>
       </c>
       <c r="D6">
         <v>5.222589531680441</v>
       </c>
       <c r="E6">
-        <v>12.47422680412371</v>
+        <v>22.37800687285224</v>
       </c>
       <c r="F6">
         <v>65.14776632302406</v>
       </c>
       <c r="G6">
-        <v>22.37800687285224</v>
+        <v>12.47422680412371</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>33.48480545299631</v>
+      </c>
+      <c r="C7">
         <v>27.71655779608066</v>
-      </c>
-      <c r="C7">
-        <v>33.48480545299631</v>
       </c>
       <c r="D7">
         <v>3.607951634388769</v>
       </c>
       <c r="E7">
-        <v>17.19374900896774</v>
+        <v>20.77203615285682</v>
       </c>
       <c r="F7">
         <v>62.03421483817544</v>
       </c>
       <c r="G7">
-        <v>20.77203615285682</v>
+        <v>17.19374900896774</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>35.22367030644593</v>
+      </c>
+      <c r="C8">
         <v>40.04931313842903</v>
-      </c>
-      <c r="C8">
-        <v>35.22367030644593</v>
       </c>
       <c r="D8">
         <v>2.496921723834653</v>
       </c>
       <c r="E8">
-        <v>22.84967845659164</v>
+        <v>20.09646302250804</v>
       </c>
       <c r="F8">
         <v>57.05385852090032</v>
       </c>
       <c r="G8">
-        <v>20.09646302250804</v>
+        <v>22.84967845659164</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>33.58256782738731</v>
+      </c>
+      <c r="C9">
         <v>27.49412518692587</v>
-      </c>
-      <c r="C9">
-        <v>33.58256782738731</v>
       </c>
       <c r="D9">
         <v>3.637140637140637</v>
       </c>
       <c r="E9">
-        <v>17.06896551724138</v>
+        <v>20.84880636604774</v>
       </c>
       <c r="F9">
         <v>62.08222811671087</v>
       </c>
       <c r="G9">
-        <v>20.84880636604774</v>
+        <v>17.06896551724138</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>31.75494917067951</v>
+      </c>
+      <c r="C10">
         <v>29.21348314606741</v>
-      </c>
-      <c r="C10">
-        <v>31.75494917067951</v>
       </c>
       <c r="D10">
         <v>3.423076923076923</v>
       </c>
       <c r="E10">
-        <v>18.14857902609274</v>
+        <v>19.72743892305136</v>
       </c>
       <c r="F10">
         <v>62.12398205085591</v>
       </c>
       <c r="G10">
-        <v>19.72743892305136</v>
+        <v>18.14857902609274</v>
       </c>
     </row>
   </sheetData>
